--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/20gps/5mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/20gps/5mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X46"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24">
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.59013643519</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>684.7127488521322</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>680.0717004874964</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24">
+        <v>0.246141818</v>
+      </c>
+      <c r="Y2">
+        <v>0.261588174</v>
+      </c>
+      <c r="Z2">
+        <v>0.3591854219550112</v>
+      </c>
+      <c r="AA2">
+        <v>7.723177999999997</v>
+      </c>
+      <c r="AB2">
+        <v>0.04757041304768599</v>
+      </c>
+      <c r="AC2">
+        <v>32.57206828191241</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.59025275463</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>677.4213878773591</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24">
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>679.8819109525917</v>
+      </c>
+      <c r="X3">
+        <v>0.246183416</v>
+      </c>
+      <c r="Y3">
+        <v>0.261602816</v>
+      </c>
+      <c r="Z3">
+        <v>0.3592245922157319</v>
+      </c>
+      <c r="AA3">
+        <v>7.709700000000005</v>
+      </c>
+      <c r="AB3">
+        <v>0.0476548706758091</v>
+      </c>
+      <c r="AC3">
+        <v>32.28242863232266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.59036849537</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>678.1562421179837</v>
       </c>
-      <c r="V4">
-        <v>4.014385303180391</v>
-      </c>
-      <c r="W4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24">
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.246229144</v>
+      </c>
+      <c r="Y4">
+        <v>0.261611728</v>
+      </c>
+      <c r="Z4">
+        <v>0.3592624216114437</v>
+      </c>
+      <c r="AA4">
+        <v>7.691291999999997</v>
+      </c>
+      <c r="AB4">
+        <v>0.04776871868884831</v>
+      </c>
+      <c r="AC4">
+        <v>32.39465475682047</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.59048481481</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>678.0324027623006</v>
       </c>
-      <c r="V5">
-        <v>0.393422192773235</v>
-      </c>
-      <c r="W5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24">
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>32.51764504822712</v>
+      </c>
+      <c r="X5">
+        <v>0.246257088</v>
+      </c>
+      <c r="Y5">
+        <v>0.261622868</v>
+      </c>
+      <c r="Z5">
+        <v>0.3592896859788563</v>
+      </c>
+      <c r="AA5">
+        <v>7.68289</v>
+      </c>
+      <c r="AB5">
+        <v>0.04782214059404118</v>
+      </c>
+      <c r="AC5">
+        <v>32.42496089221429</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.59060113426</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>677.2866598201637</v>
       </c>
-      <c r="V6">
-        <v>0.470397366496999</v>
-      </c>
-      <c r="W6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24">
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>0.246284398</v>
+      </c>
+      <c r="Y6">
+        <v>0.26161682</v>
+      </c>
+      <c r="Z6">
+        <v>0.3593040010981436</v>
+      </c>
+      <c r="AA6">
+        <v>7.666211000000004</v>
+      </c>
+      <c r="AB6">
+        <v>0.04792346633710661</v>
+      </c>
+      <c r="AC6">
+        <v>32.45792444246299</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.590716875</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>679.5739480419429</v>
       </c>
-      <c r="V7">
-        <v>1.166489162288805</v>
-      </c>
-      <c r="W7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24">
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>0.246300276</v>
+      </c>
+      <c r="Y7">
+        <v>0.261619048</v>
+      </c>
+      <c r="Z7">
+        <v>0.3593165070437239</v>
+      </c>
+      <c r="AA7">
+        <v>7.659386000000005</v>
+      </c>
+      <c r="AB7">
+        <v>0.0479659075195759</v>
+      </c>
+      <c r="AC7">
+        <v>32.59638114449291</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.59083319444</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>677.1811598269596</v>
       </c>
-      <c r="V8">
-        <v>1.352051102326727</v>
-      </c>
-      <c r="W8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24">
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>0.246308214</v>
+      </c>
+      <c r="Y8">
+        <v>0.261628278</v>
+      </c>
+      <c r="Z8">
+        <v>0.3593286686769023</v>
+      </c>
+      <c r="AA8">
+        <v>7.660031999999994</v>
+      </c>
+      <c r="AB8">
+        <v>0.04796359097972095</v>
+      </c>
+      <c r="AC8">
+        <v>32.48004016911333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.59094951389</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>681.4179116064881</v>
       </c>
-      <c r="V9">
-        <v>2.124292145259667</v>
-      </c>
-      <c r="W9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24">
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>0.246312342</v>
+      </c>
+      <c r="Y9">
+        <v>0.261640374</v>
+      </c>
+      <c r="Z9">
+        <v>0.3593403054604157</v>
+      </c>
+      <c r="AA9">
+        <v>7.664015999999997</v>
+      </c>
+      <c r="AB9">
+        <v>0.04794122701629914</v>
+      </c>
+      <c r="AC9">
+        <v>32.66801079329911</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.59106525463</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>676.2668342922063</v>
       </c>
-      <c r="V10">
-        <v>2.748322346527895</v>
-      </c>
-      <c r="W10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24">
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>0.24631266</v>
+      </c>
+      <c r="Y10">
+        <v>0.261653742</v>
+      </c>
+      <c r="Z10">
+        <v>0.3593502569623099</v>
+      </c>
+      <c r="AA10">
+        <v>7.670541</v>
+      </c>
+      <c r="AB10">
+        <v>0.04790348935199417</v>
+      </c>
+      <c r="AC10">
+        <v>32.39554109562351</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.59118157408</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>677.3830267140248</v>
       </c>
-      <c r="V11">
-        <v>2.709851752269283</v>
-      </c>
-      <c r="W11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24">
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>0.246312342</v>
+      </c>
+      <c r="Y11">
+        <v>0.26167475</v>
+      </c>
+      <c r="Z11">
+        <v>0.3593653358479188</v>
+      </c>
+      <c r="AA11">
+        <v>7.681204000000001</v>
+      </c>
+      <c r="AB11">
+        <v>0.04784180957124504</v>
+      </c>
+      <c r="AC11">
+        <v>32.40722977084597</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.59129731482</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>680.4138591657158</v>
       </c>
-      <c r="V12">
-        <v>2.145912633133605</v>
-      </c>
-      <c r="W12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24">
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>0.246313294</v>
+      </c>
+      <c r="Y12">
+        <v>0.261682708</v>
+      </c>
+      <c r="Z12">
+        <v>0.3593717830706018</v>
+      </c>
+      <c r="AA12">
+        <v>7.684707000000003</v>
+      </c>
+      <c r="AB12">
+        <v>0.04782177477633295</v>
+      </c>
+      <c r="AC12">
+        <v>32.53859832771839</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.59141305555</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>682.0940127783215</v>
       </c>
-      <c r="V13">
-        <v>2.387545853317993</v>
-      </c>
-      <c r="W13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24">
+      <c r="V13" t="b">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>0.246339334</v>
+      </c>
+      <c r="Y13">
+        <v>0.261699896</v>
+      </c>
+      <c r="Z13">
+        <v>0.3594021466852617</v>
+      </c>
+      <c r="AA13">
+        <v>7.680281000000001</v>
+      </c>
+      <c r="AB13">
+        <v>0.0478519949817399</v>
+      </c>
+      <c r="AC13">
+        <v>32.63955927654307</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.591529375</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>681.222996058458</v>
       </c>
-      <c r="V14">
-        <v>0.8402667036359367</v>
-      </c>
-      <c r="W14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24">
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>0.246358706</v>
+      </c>
+      <c r="Y14">
+        <v>0.261710082</v>
+      </c>
+      <c r="Z14">
+        <v>0.3594228415702613</v>
+      </c>
+      <c r="AA14">
+        <v>7.675688000000001</v>
+      </c>
+      <c r="AB14">
+        <v>0.04788201536766051</v>
+      </c>
+      <c r="AC14">
+        <v>32.61832996607482</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.59164569445</v>
       </c>
@@ -1482,14 +1728,29 @@
       <c r="U15">
         <v>678.8250276086571</v>
       </c>
-      <c r="V15">
-        <v>1.692886433088567</v>
-      </c>
-      <c r="W15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24">
+      <c r="V15" t="b">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>0.246364422</v>
+      </c>
+      <c r="Y15">
+        <v>0.261716448</v>
+      </c>
+      <c r="Z15">
+        <v>0.3594313948184421</v>
+      </c>
+      <c r="AA15">
+        <v>7.676012999999998</v>
+      </c>
+      <c r="AB15">
+        <v>0.04788116619435767</v>
+      </c>
+      <c r="AC15">
+        <v>32.50293396381954</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>46068.59176143519</v>
       </c>
@@ -1553,14 +1814,29 @@
       <c r="U16">
         <v>675.7198470449932</v>
       </c>
-      <c r="V16">
-        <v>2.759137790554501</v>
-      </c>
-      <c r="W16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23">
+      <c r="V16" t="b">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>0.246386016</v>
+      </c>
+      <c r="Y16">
+        <v>0.261723132</v>
+      </c>
+      <c r="Z16">
+        <v>0.3594510630172648</v>
+      </c>
+      <c r="AA16">
+        <v>7.668558000000004</v>
+      </c>
+      <c r="AB16">
+        <v>0.04792819287582024</v>
+      </c>
+      <c r="AC16">
+        <v>32.38603115919219</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29">
       <c r="A17" s="1">
         <v>46068.59187717592</v>
       </c>
@@ -1624,14 +1900,29 @@
       <c r="U17">
         <v>679.3643465143374</v>
       </c>
-      <c r="V17">
-        <v>1.967036162903924</v>
-      </c>
-      <c r="W17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23">
+      <c r="V17" t="b">
+        <v>1</v>
+      </c>
+      <c r="X17">
+        <v>0.246371408</v>
+      </c>
+      <c r="Y17">
+        <v>0.261734272</v>
+      </c>
+      <c r="Z17">
+        <v>0.3594491616616631</v>
+      </c>
+      <c r="AA17">
+        <v>7.681432000000001</v>
+      </c>
+      <c r="AB17">
+        <v>0.04785112334670014</v>
+      </c>
+      <c r="AC17">
+        <v>32.5083471424079</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29">
       <c r="A18" s="1">
         <v>46068.59199349537</v>
       </c>
@@ -1695,14 +1986,29 @@
       <c r="U18">
         <v>681.4096402927975</v>
       </c>
-      <c r="V18">
-        <v>2.88211005529562</v>
-      </c>
-      <c r="W18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23">
+      <c r="V18" t="b">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>0.246339018</v>
+      </c>
+      <c r="Y18">
+        <v>0.261745094</v>
+      </c>
+      <c r="Z18">
+        <v>0.3594348425268106</v>
+      </c>
+      <c r="AA18">
+        <v>7.703037999999999</v>
+      </c>
+      <c r="AB18">
+        <v>0.04772095920454407</v>
+      </c>
+      <c r="AC18">
+        <v>32.51752164599564</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29">
       <c r="A19" s="1">
         <v>46068.59210923611</v>
       </c>
@@ -1766,14 +2072,29 @@
       <c r="U19">
         <v>680.4001125196964</v>
       </c>
-      <c r="V19">
-        <v>1.022674938802478</v>
-      </c>
-      <c r="W19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23">
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>0.246338382</v>
+      </c>
+      <c r="Y19">
+        <v>0.261753688</v>
+      </c>
+      <c r="Z19">
+        <v>0.3594406649615194</v>
+      </c>
+      <c r="AA19">
+        <v>7.707653000000001</v>
+      </c>
+      <c r="AB19">
+        <v>0.0476943796946681</v>
+      </c>
+      <c r="AC19">
+        <v>32.4512613108093</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29">
       <c r="A20" s="1">
         <v>46068.59222555556</v>
       </c>
@@ -1837,14 +2158,29 @@
       <c r="U20">
         <v>679.8718220410857</v>
       </c>
-      <c r="V20">
-        <v>0.7813580197058181</v>
-      </c>
-      <c r="W20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23">
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>0.246341876</v>
+      </c>
+      <c r="Y20">
+        <v>0.261762602</v>
+      </c>
+      <c r="Z20">
+        <v>0.3594495509484048</v>
+      </c>
+      <c r="AA20">
+        <v>7.710363000000001</v>
+      </c>
+      <c r="AB20">
+        <v>0.04767948020703708</v>
+      </c>
+      <c r="AC20">
+        <v>32.41593508233018</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29">
       <c r="A21" s="1">
         <v>46068.592341875</v>
       </c>
@@ -1908,14 +2244,29 @@
       <c r="U21">
         <v>682.7375548756918</v>
       </c>
-      <c r="V21">
-        <v>1.52507662521879</v>
-      </c>
-      <c r="W21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23">
+      <c r="V21" t="b">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>0.246376488</v>
+      </c>
+      <c r="Y21">
+        <v>0.261766738</v>
+      </c>
+      <c r="Z21">
+        <v>0.3594762842836434</v>
+      </c>
+      <c r="AA21">
+        <v>7.695125000000004</v>
+      </c>
+      <c r="AB21">
+        <v>0.04777314365390941</v>
+      </c>
+      <c r="AC21">
+        <v>32.61651928699528</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29">
       <c r="A22" s="1">
         <v>46068.59245819444</v>
       </c>
@@ -1979,14 +2330,29 @@
       <c r="U22">
         <v>684.9110344813818</v>
       </c>
-      <c r="V22">
-        <v>2.527518555623497</v>
-      </c>
-      <c r="W22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23">
+      <c r="V22" t="b">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>0.246395224</v>
+      </c>
+      <c r="Y22">
+        <v>0.261776924</v>
+      </c>
+      <c r="Z22">
+        <v>0.3594965428886792</v>
+      </c>
+      <c r="AA22">
+        <v>7.690849999999998</v>
+      </c>
+      <c r="AB22">
+        <v>0.04780111121780752</v>
+      </c>
+      <c r="AC22">
+        <v>32.73950853354813</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29">
       <c r="A23" s="1">
         <v>46068.59257393519</v>
       </c>
@@ -2050,14 +2416,29 @@
       <c r="U23">
         <v>679.7074290115487</v>
       </c>
-      <c r="V23">
-        <v>2.613528465331186</v>
-      </c>
-      <c r="W23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23">
+      <c r="V23" t="b">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>0.246415232</v>
+      </c>
+      <c r="Y23">
+        <v>0.261788384</v>
+      </c>
+      <c r="Z23">
+        <v>0.3595186011306581</v>
+      </c>
+      <c r="AA23">
+        <v>7.686575999999995</v>
+      </c>
+      <c r="AB23">
+        <v>0.04782933364344182</v>
+      </c>
+      <c r="AC23">
+        <v>32.50995340211941</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29">
       <c r="A24" s="1">
         <v>46068.59269025463</v>
       </c>
@@ -2121,14 +2502,29 @@
       <c r="U24">
         <v>678.9985778374588</v>
       </c>
-      <c r="V24">
-        <v>3.228444502619284</v>
-      </c>
-      <c r="W24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23">
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>0.24642984</v>
+      </c>
+      <c r="Y24">
+        <v>0.261789656</v>
+      </c>
+      <c r="Z24">
+        <v>0.3595295398587214</v>
+      </c>
+      <c r="AA24">
+        <v>7.679907999999998</v>
+      </c>
+      <c r="AB24">
+        <v>0.04787043933514909</v>
+      </c>
+      <c r="AC24">
+        <v>32.50396022902058</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29">
       <c r="A25" s="1">
         <v>46068.59280657407</v>
       </c>
@@ -2192,14 +2588,29 @@
       <c r="U25">
         <v>683.273713327203</v>
       </c>
-      <c r="V25">
-        <v>2.291201913944001</v>
-      </c>
-      <c r="W25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23">
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="X25">
+        <v>0.246445082</v>
+      </c>
+      <c r="Y25">
+        <v>0.26180207</v>
+      </c>
+      <c r="Z25">
+        <v>0.3595490262791315</v>
+      </c>
+      <c r="AA25">
+        <v>7.678494000000001</v>
+      </c>
+      <c r="AB25">
+        <v>0.04788135188311603</v>
+      </c>
+      <c r="AC25">
+        <v>32.71606910030315</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29">
       <c r="A26" s="1">
         <v>46068.59292231481</v>
       </c>
@@ -2263,14 +2674,29 @@
       <c r="U26">
         <v>679.4831887938378</v>
       </c>
-      <c r="V26">
-        <v>2.340929568667084</v>
-      </c>
-      <c r="W26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23">
+      <c r="V26" t="b">
+        <v>1</v>
+      </c>
+      <c r="X26">
+        <v>0.246453974</v>
+      </c>
+      <c r="Y26">
+        <v>0.261814166</v>
+      </c>
+      <c r="Z26">
+        <v>0.3595639286951184</v>
+      </c>
+      <c r="AA26">
+        <v>7.680095999999999</v>
+      </c>
+      <c r="AB26">
+        <v>0.0478736975313219</v>
+      </c>
+      <c r="AC26">
+        <v>32.52937265793429</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29">
       <c r="A27" s="1">
         <v>46068.59303863426</v>
       </c>
@@ -2334,14 +2760,29 @@
       <c r="U27">
         <v>677.5464453513229</v>
       </c>
-      <c r="V27">
-        <v>2.913206991950994</v>
-      </c>
-      <c r="W27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23">
+      <c r="V27" t="b">
+        <v>1</v>
+      </c>
+      <c r="X27">
+        <v>0.24645715</v>
+      </c>
+      <c r="Y27">
+        <v>0.26181735</v>
+      </c>
+      <c r="Z27">
+        <v>0.3595684240129339</v>
+      </c>
+      <c r="AA27">
+        <v>7.680100000000003</v>
+      </c>
+      <c r="AB27">
+        <v>0.04787424609392334</v>
+      </c>
+      <c r="AC27">
+        <v>32.43702526481221</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29">
       <c r="A28" s="1">
         <v>46068.593154375</v>
       </c>
@@ -2405,14 +2846,29 @@
       <c r="U28">
         <v>682.5797391025217</v>
       </c>
-      <c r="V28">
-        <v>2.538820098726747</v>
-      </c>
-      <c r="W28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23">
+      <c r="V28" t="b">
+        <v>1</v>
+      </c>
+      <c r="X28">
+        <v>0.246464772</v>
+      </c>
+      <c r="Y28">
+        <v>0.261814802</v>
+      </c>
+      <c r="Z28">
+        <v>0.3595717930863198</v>
+      </c>
+      <c r="AA28">
+        <v>7.675015000000002</v>
+      </c>
+      <c r="AB28">
+        <v>0.04790501048702325</v>
+      </c>
+      <c r="AC28">
+        <v>32.6989895599359</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29">
       <c r="A29" s="1">
         <v>46068.59327011574</v>
       </c>
@@ -2476,14 +2932,29 @@
       <c r="U29">
         <v>682.6009203948367</v>
       </c>
-      <c r="V29">
-        <v>2.9121072724778</v>
-      </c>
-      <c r="W29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23">
+      <c r="V29" t="b">
+        <v>1</v>
+      </c>
+      <c r="X29">
+        <v>0.246442224</v>
+      </c>
+      <c r="Y29">
+        <v>0.261824352</v>
+      </c>
+      <c r="Z29">
+        <v>0.3595632921618752</v>
+      </c>
+      <c r="AA29">
+        <v>7.691064000000004</v>
+      </c>
+      <c r="AB29">
+        <v>0.0478083261809931</v>
+      </c>
+      <c r="AC29">
+        <v>32.63400745368246</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29">
       <c r="A30" s="1">
         <v>46068.59338643518</v>
       </c>
@@ -2547,14 +3018,29 @@
       <c r="U30">
         <v>682.8998120806297</v>
       </c>
-      <c r="V30">
-        <v>0.1789932951725196</v>
-      </c>
-      <c r="W30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23">
+      <c r="V30" t="b">
+        <v>1</v>
+      </c>
+      <c r="X30">
+        <v>0.246422536</v>
+      </c>
+      <c r="Y30">
+        <v>0.261826262</v>
+      </c>
+      <c r="Z30">
+        <v>0.3595511892923787</v>
+      </c>
+      <c r="AA30">
+        <v>7.701863000000003</v>
+      </c>
+      <c r="AB30">
+        <v>0.04774269099006903</v>
+      </c>
+      <c r="AC30">
+        <v>32.60347470534171</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29">
       <c r="A31" s="1">
         <v>46068.59350217593</v>
       </c>
@@ -2618,14 +3104,29 @@
       <c r="U31">
         <v>681.3623103161511</v>
       </c>
-      <c r="V31">
-        <v>0.815209875087039</v>
-      </c>
-      <c r="W31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23">
+      <c r="V31" t="b">
+        <v>1</v>
+      </c>
+      <c r="X31">
+        <v>0.24644413</v>
+      </c>
+      <c r="Y31">
+        <v>0.261841222</v>
+      </c>
+      <c r="Z31">
+        <v>0.3595768829470412</v>
+      </c>
+      <c r="AA31">
+        <v>7.698546</v>
+      </c>
+      <c r="AB31">
+        <v>0.0477656226591436</v>
+      </c>
+      <c r="AC31">
+        <v>32.54569500872358</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29">
       <c r="A32" s="1">
         <v>46068.59361849537</v>
       </c>
@@ -2689,14 +3190,29 @@
       <c r="U32">
         <v>679.6779658813534</v>
       </c>
-      <c r="V32">
-        <v>1.611480726050886</v>
-      </c>
-      <c r="W32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23">
+      <c r="V32" t="b">
+        <v>1</v>
+      </c>
+      <c r="X32">
+        <v>0.246458738</v>
+      </c>
+      <c r="Y32">
+        <v>0.261848862</v>
+      </c>
+      <c r="Z32">
+        <v>0.359592458301405</v>
+      </c>
+      <c r="AA32">
+        <v>7.695062</v>
+      </c>
+      <c r="AB32">
+        <v>0.04778828051079098</v>
+      </c>
+      <c r="AC32">
+        <v>32.48064129054194</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29">
       <c r="A33" s="1">
         <v>46068.59373481481</v>
       </c>
@@ -2760,14 +3276,29 @@
       <c r="U33">
         <v>679.0729724354693</v>
       </c>
-      <c r="V33">
-        <v>1.186317915268376</v>
-      </c>
-      <c r="W33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23">
+      <c r="V33" t="b">
+        <v>1</v>
+      </c>
+      <c r="X33">
+        <v>0.246477474</v>
+      </c>
+      <c r="Y33">
+        <v>0.26186223</v>
+      </c>
+      <c r="Z33">
+        <v>0.3596150340155339</v>
+      </c>
+      <c r="AA33">
+        <v>7.692377999999998</v>
+      </c>
+      <c r="AB33">
+        <v>0.04780709452585493</v>
+      </c>
+      <c r="AC33">
+        <v>32.46450578317576</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29">
       <c r="A34" s="1">
         <v>46068.59385055555</v>
       </c>
@@ -2831,14 +3362,29 @@
       <c r="U34">
         <v>676.9049199678102</v>
       </c>
-      <c r="V34">
-        <v>1.458095345001961</v>
-      </c>
-      <c r="W34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23">
+      <c r="V34" t="b">
+        <v>1</v>
+      </c>
+      <c r="X34">
+        <v>0.246489858</v>
+      </c>
+      <c r="Y34">
+        <v>0.261874326</v>
+      </c>
+      <c r="Z34">
+        <v>0.3596323299076634</v>
+      </c>
+      <c r="AA34">
+        <v>7.692233999999999</v>
+      </c>
+      <c r="AB34">
+        <v>0.04781014907743079</v>
+      </c>
+      <c r="AC34">
+        <v>32.36292513490736</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29">
       <c r="A35" s="1">
         <v>46068.593966875</v>
       </c>
@@ -2902,14 +3448,29 @@
       <c r="U35">
         <v>676.9368255340871</v>
       </c>
-      <c r="V35">
-        <v>1.242617737678396</v>
-      </c>
-      <c r="W35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23">
+      <c r="V35" t="b">
+        <v>1</v>
+      </c>
+      <c r="X35">
+        <v>0.246500974</v>
+      </c>
+      <c r="Y35">
+        <v>0.261872098</v>
+      </c>
+      <c r="Z35">
+        <v>0.3596383265085498</v>
+      </c>
+      <c r="AA35">
+        <v>7.685561999999997</v>
+      </c>
+      <c r="AB35">
+        <v>0.04785060208460266</v>
+      </c>
+      <c r="AC35">
+        <v>32.39183467504569</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29">
       <c r="A36" s="1">
         <v>46068.59408261574</v>
       </c>
@@ -2973,14 +3534,29 @@
       <c r="U36">
         <v>679.1563279249377</v>
       </c>
-      <c r="V36">
-        <v>1.290739233770003</v>
-      </c>
-      <c r="W36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23">
+      <c r="V36" t="b">
+        <v>1</v>
+      </c>
+      <c r="X36">
+        <v>0.24649494</v>
+      </c>
+      <c r="Y36">
+        <v>0.261881648</v>
+      </c>
+      <c r="Z36">
+        <v>0.3596411447607177</v>
+      </c>
+      <c r="AA36">
+        <v>7.693353999999999</v>
+      </c>
+      <c r="AB36">
+        <v>0.04780461380954162</v>
+      </c>
+      <c r="AC36">
+        <v>32.46680597275806</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29">
       <c r="A37" s="1">
         <v>46068.59419893518</v>
       </c>
@@ -3044,14 +3620,29 @@
       <c r="U37">
         <v>681.1572652027897</v>
       </c>
-      <c r="V37">
-        <v>2.11116286479134</v>
-      </c>
-      <c r="W37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23">
+      <c r="V37" t="b">
+        <v>1</v>
+      </c>
+      <c r="X37">
+        <v>0.24649367</v>
+      </c>
+      <c r="Y37">
+        <v>0.261893744</v>
+      </c>
+      <c r="Z37">
+        <v>0.359649082435096</v>
+      </c>
+      <c r="AA37">
+        <v>7.700037000000002</v>
+      </c>
+      <c r="AB37">
+        <v>0.04776594765312227</v>
+      </c>
+      <c r="AC37">
+        <v>32.53612227322038</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29">
       <c r="A38" s="1">
         <v>46068.59431525463</v>
       </c>
@@ -3115,14 +3706,29 @@
       <c r="U38">
         <v>682.191918380484</v>
       </c>
-      <c r="V38">
-        <v>1.543214534762605</v>
-      </c>
-      <c r="W38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23">
+      <c r="V38" t="b">
+        <v>1</v>
+      </c>
+      <c r="X38">
+        <v>0.246508912</v>
+      </c>
+      <c r="Y38">
+        <v>0.261906158</v>
+      </c>
+      <c r="Z38">
+        <v>0.3596685686764201</v>
+      </c>
+      <c r="AA38">
+        <v>7.698623000000005</v>
+      </c>
+      <c r="AB38">
+        <v>0.04777681136756638</v>
+      </c>
+      <c r="AC38">
+        <v>32.59295460094263</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29">
       <c r="A39" s="1">
         <v>46068.59443157407</v>
       </c>
@@ -3186,14 +3792,29 @@
       <c r="U39">
         <v>683.9118051933146</v>
       </c>
-      <c r="V39">
-        <v>1.391402673950969</v>
-      </c>
-      <c r="W39" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23">
+      <c r="V39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X39">
+        <v>0.24651177</v>
+      </c>
+      <c r="Y39">
+        <v>0.261917298</v>
+      </c>
+      <c r="Z39">
+        <v>0.3596786395383436</v>
+      </c>
+      <c r="AA39">
+        <v>7.702764000000002</v>
+      </c>
+      <c r="AB39">
+        <v>0.04775353055623823</v>
+      </c>
+      <c r="AC39">
+        <v>32.659203287071</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29">
       <c r="A40" s="1">
         <v>46068.59454731482</v>
       </c>
@@ -3257,14 +3878,29 @@
       <c r="U40">
         <v>675.7608741733767</v>
       </c>
-      <c r="V40">
-        <v>4.296394161280378</v>
-      </c>
-      <c r="W40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23">
+      <c r="V40" t="b">
+        <v>1</v>
+      </c>
+      <c r="X40">
+        <v>0.246514946</v>
+      </c>
+      <c r="Y40">
+        <v>0.261923346</v>
+      </c>
+      <c r="Z40">
+        <v>0.3596852204097614</v>
+      </c>
+      <c r="AA40">
+        <v>7.7042</v>
+      </c>
+      <c r="AB40">
+        <v>0.047745855290464</v>
+      </c>
+      <c r="AC40">
+        <v>32.2647809092395</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29">
       <c r="A41" s="1">
         <v>46068.59466363426</v>
       </c>
@@ -3328,14 +3964,29 @@
       <c r="U41">
         <v>677.3881480888632</v>
       </c>
-      <c r="V41">
-        <v>4.313617949862678</v>
-      </c>
-      <c r="W41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23">
+      <c r="V41" t="b">
+        <v>1</v>
+      </c>
+      <c r="X41">
+        <v>0.24655115</v>
+      </c>
+      <c r="Y41">
+        <v>0.261929076</v>
+      </c>
+      <c r="Z41">
+        <v>0.3597142065870297</v>
+      </c>
+      <c r="AA41">
+        <v>7.688962999999994</v>
+      </c>
+      <c r="AB41">
+        <v>0.04784001192191896</v>
+      </c>
+      <c r="AC41">
+        <v>32.40625708033782</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29">
       <c r="A42" s="1">
         <v>46068.5947799537</v>
       </c>
@@ -3399,14 +4050,29 @@
       <c r="U42">
         <v>681.2199450786306</v>
       </c>
-      <c r="V42">
-        <v>2.802741030830262</v>
-      </c>
-      <c r="W42" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23">
+      <c r="V42" t="b">
+        <v>1</v>
+      </c>
+      <c r="X42">
+        <v>0.246590528</v>
+      </c>
+      <c r="Y42">
+        <v>0.261934486</v>
+      </c>
+      <c r="Z42">
+        <v>0.3597451368057711</v>
+      </c>
+      <c r="AA42">
+        <v>7.671979</v>
+      </c>
+      <c r="AB42">
+        <v>0.04794523907621938</v>
+      </c>
+      <c r="AC42">
+        <v>32.66125313028398</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29">
       <c r="A43" s="1">
         <v>46068.59489569444</v>
       </c>
@@ -3470,14 +4136,29 @@
       <c r="U43">
         <v>676.329741390104</v>
       </c>
-      <c r="V43">
-        <v>2.57283841395847</v>
-      </c>
-      <c r="W43" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23">
+      <c r="V43" t="b">
+        <v>1</v>
+      </c>
+      <c r="X43">
+        <v>0.246603548</v>
+      </c>
+      <c r="Y43">
+        <v>0.261937034</v>
+      </c>
+      <c r="Z43">
+        <v>0.3597559167920737</v>
+      </c>
+      <c r="AA43">
+        <v>7.666742999999997</v>
+      </c>
+      <c r="AB43">
+        <v>0.04797793448126048</v>
+      </c>
+      <c r="AC43">
+        <v>32.44890402014225</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29">
       <c r="A44" s="1">
         <v>46068.59501143519</v>
       </c>
@@ -3541,14 +4222,29 @@
       <c r="U44">
         <v>680.1524793618786</v>
       </c>
-      <c r="V44">
-        <v>2.571215690828117</v>
-      </c>
-      <c r="W44" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23">
+      <c r="V44" t="b">
+        <v>1</v>
+      </c>
+      <c r="X44">
+        <v>0.246568932</v>
+      </c>
+      <c r="Y44">
+        <v>0.26193385</v>
+      </c>
+      <c r="Z44">
+        <v>0.3597298708801414</v>
+      </c>
+      <c r="AA44">
+        <v>7.682459000000001</v>
+      </c>
+      <c r="AB44">
+        <v>0.04788073852512655</v>
+      </c>
+      <c r="AC44">
+        <v>32.56620302154264</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29">
       <c r="A45" s="1">
         <v>46068.59512775463</v>
       </c>
@@ -3612,14 +4308,29 @@
       <c r="U45">
         <v>681.5055538880639</v>
       </c>
-      <c r="V45">
-        <v>2.684311559422461</v>
-      </c>
-      <c r="W45" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23">
+      <c r="V45" t="b">
+        <v>1</v>
+      </c>
+      <c r="X45">
+        <v>0.246573062</v>
+      </c>
+      <c r="Y45">
+        <v>0.261932896</v>
+      </c>
+      <c r="Z45">
+        <v>0.359732007070545</v>
+      </c>
+      <c r="AA45">
+        <v>7.679917000000003</v>
+      </c>
+      <c r="AB45">
+        <v>0.04789616756752502</v>
+      </c>
+      <c r="AC45">
+        <v>32.64150420722166</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29">
       <c r="A46" s="1">
         <v>46068.59524349537</v>
       </c>
@@ -3683,11 +4394,26 @@
       <c r="U46">
         <v>680.4645388572561</v>
       </c>
-      <c r="V46">
-        <v>0.7085083034610117</v>
-      </c>
-      <c r="W46" t="b">
-        <v>1</v>
+      <c r="V46" t="b">
+        <v>1</v>
+      </c>
+      <c r="X46">
+        <v>0.246567028</v>
+      </c>
+      <c r="Y46">
+        <v>0.261943718</v>
+      </c>
+      <c r="Z46">
+        <v>0.3597357512069329</v>
+      </c>
+      <c r="AA46">
+        <v>7.688345000000005</v>
+      </c>
+      <c r="AB46">
+        <v>0.0478464297082267</v>
+      </c>
+      <c r="AC46">
+        <v>32.5577987273746</v>
       </c>
     </row>
   </sheetData>
